--- a/Unity/Assets/Config/Excel/Datas/StartConfig/Benchmark/StartZoneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/StartConfig/Benchmark/StartZoneConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\ET\Unity\Assets\Config\Excel\Datas\StartConfig\Benchmark\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChangeConfig\Benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67AD139F-4267-42EE-BC2A-19EA72A55487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD074CE4-ABB8-4064-99B9-FF86B06B4DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,35 +115,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF006100"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -183,18 +154,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -209,6 +173,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -217,16 +184,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="差 2" xfId="2" xr:uid="{A530937A-DED5-4BA3-AA21-7F09D2DCCE1E}"/>
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="4" xr:uid="{BB29AEF2-D81A-48B3-A96D-3ED2CC1E1339}"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
-    <cellStyle name="好 2" xfId="3" xr:uid="{03E639D5-FA7B-40F9-B91D-B8EF583350F0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -544,55 +505,55 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="10"/>
+      <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
